--- a/수련지도_입력양식_인턴.xlsx
+++ b/수련지도_입력양식_인턴.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>총 14건 (분야: 수련·근무 13, 학습·역량 5, 진로·진학 10, 생활·심리 5, 분야 미기재 1)</t>
+          <t>총 25건 (분야: 수련·근무 24, 학습·역량 11, 진로·진학 21, 생활·심리 15, 분야 미기재 1)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="91" customHeight="1" s="21">
+    <row r="7" ht="125" customHeight="1" s="21">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>’26.8월</t>
@@ -776,10 +776,10 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>총 15건
-· 현장 교육 8건: 산부인과 병동·수술·외래 예진, 정형외과 수술방 scrub·부목 적용, 성형외과 수술실 마취 전 평가·환자안전
+          <t>총 23건
+· 현장 교육 12건: 산부인과 병동·수술·외래 예진, 정형외과 수술방 scrub·부목 적용, 성형외과 수술실 마취 전 평가·환자안전, 응급실 bedside teaching·기본 술기
 · 임상 교육 6건: 내과·외과 인턴 역량평가(기본 술기, 외래 예진, 상급자 보고)
-· 이론 교육 1건: 전체 인턴 교육(의사과학자 양성 프로그램 소개)</t>
+· 이론 교육 5건: 전체 인턴 교육(의사과학자 양성 프로그램 소개), 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" s="21">
+    <row r="10" ht="40" customHeight="1" s="21">
       <c r="A10" s="23" t="n"/>
       <c r="B10" s="7" t="n">
         <v>4</v>
@@ -827,7 +827,7 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>총 15건 (분야: 수련·근무 13, 학습·역량 3, 진로·진학 14, 생활·심리 7)</t>
+          <t>총 27건 (분야: 수련·근무 23, 학습·역량 11, 진로·진학 26, 생활·심리 18)</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="125" customHeight="1" s="21">
+    <row r="12" ht="142" customHeight="1" s="21">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>’26.9월</t>
@@ -863,10 +863,10 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>총 39건
-· 현장 교육 8건: 산부인과 수술실·병동, 정형외과 수술방 무균술·C-arm, 성형외과·마취 수술실 환자안전
+          <t>총 45건
+· 현장 교육 10건: 산부인과 수술실·병동, 정형외과 수술방 무균술·C-arm, 성형외과·마취 수술실 환자안전, 응급실 초진·신경학적 진찰
 · 임상 교육 26건: 영상의학 판독·초음파 교육(복부 CT·MRI, 간·담도·췌장 등), 소아청소년과 인턴 종합평가, 내과·외과 인턴 역량평가
-· 이론 교육 5건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호)</t>
+· 이론 교육 9건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="21">
+    <row r="15" ht="40" customHeight="1" s="21">
       <c r="A15" s="23" t="n"/>
       <c r="B15" s="7" t="n">
         <v>4</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>총 18건 (분야: 수련·근무 17, 학습·역량 5, 진로·진학 17, 생활·심리 8)</t>
+          <t>총 28건 (분야: 수련·근무 27, 학습·역량 12, 진로·진학 27, 생활·심리 16)</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="19.5" customHeight="1" s="21">
+    <row r="4" ht="114" customHeight="1" s="21">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1064,11 +1064,28 @@
           <t>정수</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="15" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" s="21">
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>이여진, 조유민, 조정욱, 김현석, 조융, 권도균</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+8월 수련지도 : 1건 (이론 교육 1)
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+9월 수련지도 : 1건 (이론 교육 1)
+9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+합계 : 8건</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="95" customHeight="1" s="21">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1079,11 +1096,27 @@
           <t>유경헌</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="15" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="21">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>이승주, 전시형, 노하경, 임창열</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>8월 수련지도 : 2건 (현장 교육 2)
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+9월 수련지도 : 2건 (현장 교육 2)
+9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+합계 : 8건</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="114" customHeight="1" s="21">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1094,9 +1127,26 @@
           <t>윤초석</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="15" t="n"/>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>김현진, 박서연, 이단비, 권도균, 손지형, 김준섭, 김준영, 김영은, 김지유</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
+8월 수련지도 : 3건 (이론 교육 3)
+8월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
+9월 수련지도 : 3건 (이론 교육 3)
+9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
+합계 : 15건</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="133" customHeight="1" s="21">
       <c r="A7" s="11" t="inlineStr">
@@ -1163,7 +1213,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1" s="21">
+    <row r="9" ht="76" customHeight="1" s="21">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1174,9 +1224,24 @@
           <t>윤성구</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="15" t="n"/>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>김수환, 김유림, 이종현, 조윤지, 권희정, 장호세</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 1, 진로·진학 3, 생활·심리 2)
+8월 개별 면담 : 3건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 3, 생활·심리 2)
+9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 1)
+합계 : 9건</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="114" customHeight="1" s="21">
       <c r="A10" s="11" t="inlineStr">
@@ -1303,6 +1368,36 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="76" customHeight="1" s="21">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>이준철</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>유은정, 이민재, 조유민, 강혜민 외 1명(대상 미기재)</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
+8월 수련지도 : 2건 (현장 교육 2)
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2, 생활·심리 2)
+합계 : 7건</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/수련지도_입력양식_인턴.xlsx
+++ b/수련지도_입력양식_인턴.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>총 25건 (분야: 수련·근무 24, 학습·역량 11, 진로·진학 21, 생활·심리 15, 분야 미기재 1)</t>
+          <t>총 28건 (분야: 수련·근무 27, 학습·역량 11, 진로·진학 23, 생활·심리 18, 분야 미기재 1)</t>
         </is>
       </c>
     </row>
@@ -776,10 +776,10 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>총 23건
-· 현장 교육 12건: 산부인과 병동·수술·외래 예진, 정형외과 수술방 scrub·부목 적용, 성형외과 수술실 마취 전 평가·환자안전, 응급실 bedside teaching·기본 술기
+          <t>총 26건
+· 현장 교육 13건: 산부인과 병동·수술·외래 예진, 정형외과 수술방 scrub·부목 적용, 성형외과 수술실 마취 전 평가·환자안전, 응급실 bedside teaching·기본 술기, 신경외과 월간 수련지도(취합)
 · 임상 교육 6건: 내과·외과 인턴 역량평가(기본 술기, 외래 예진, 상급자 보고)
-· 이론 교육 5건: 전체 인턴 교육(의사과학자 양성 프로그램 소개), 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈</t>
+· 이론 교육 7건: 전체 인턴 교육(의사과학자 양성 프로그램 소개), 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈, 이비인후과 외래 환자 응대</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" s="21">
+    <row r="9" ht="40" customHeight="1" s="21">
       <c r="A9" s="23" t="n"/>
       <c r="B9" s="7" t="n">
         <v>3</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>총 1건: 정기 간담회: 여성 전공의 모성보호, 신규 인턴 근무시간 명확화</t>
+          <t>총 3건: 정기 간담회(여성 전공의 모성보호, 신규 인턴 근무시간 명확화), 말초성·중추성 어지럼증 감별(인턴별 2건)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>총 27건 (분야: 수련·근무 23, 학습·역량 11, 진로·진학 26, 생활·심리 18)</t>
+          <t>총 30건 (분야: 수련·근무 26, 학습·역량 11, 진로·진학 28, 생활·심리 20)</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="142" customHeight="1" s="21">
+    <row r="12" ht="159" customHeight="1" s="21">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>’26.9월</t>
@@ -863,10 +863,10 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>총 45건
-· 현장 교육 10건: 산부인과 수술실·병동, 정형외과 수술방 무균술·C-arm, 성형외과·마취 수술실 환자안전, 응급실 초진·신경학적 진찰
+          <t>총 68건
+· 현장 교육 31건: 산부인과 수술실·병동, 정형외과 수술방 무균술·C-arm, 성형외과·마취 수술실 환자안전, 응급실 초진·신경학적 진찰, 이비인후과 외래, 신경외과 병동 회진 교육(20건)
 · 임상 교육 26건: 영상의학 판독·초음파 교육(복부 CT·MRI, 간·담도·췌장 등), 소아청소년과 인턴 종합평가, 내과·외과 인턴 역량평가
-· 이론 교육 9건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응</t>
+· 이론 교육 11건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응, 이비인후과 외래 업무</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>총 1건: 정기 간담회: 냉장고 교체·여자 휴게실 환경개선, 환자경험평가, 12월 면접 응시자격</t>
+          <t>총 2건: 정기 간담회(냉장고 교체·여자 휴게실 환경개선, 환자경험평가, 12월 면접 응시자격), 이비인후과 인턴 9월 간담회</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>총 28건 (분야: 수련·근무 27, 학습·역량 12, 진로·진학 27, 생활·심리 16)</t>
+          <t>총 31건 (분야: 수련·근무 30, 학습·역량 13, 진로·진학 28, 생활·심리 19)</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1" s="21">
+    <row r="11" ht="114" customHeight="1" s="21">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1286,9 +1286,26 @@
           <t>홍승우</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="15" t="n"/>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>정문영, 최정민, 유채현, 전시형</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
+8월 수련지도 : 1건 (현장 교육 1)
+8월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
+9월 수련지도 : 20건 (현장 교육 20)
+9월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1, 생활·심리 1)
+합계 : 24건</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="114" customHeight="1" s="21">
       <c r="A12" s="11" t="inlineStr">
@@ -1322,7 +1339,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1" s="21">
+    <row r="13" ht="152" customHeight="1" s="21">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1333,9 +1350,28 @@
           <t>한상윤</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="15" t="n"/>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>이원우, 박승민, 정현도, 이예닮, 민현지, 김현진, 9월 간담회 참여 인턴</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1, 생활·심리 2)
+8월 수련지도 : 2건 (이론 교육 2)
+8월 간담회 : 2건
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1, 생활·심리 1)
+9월 수련지도 : 3건 (현장 교육 1, 이론 교육 2)
+9월 간담회 : 1건
+9월 개별 면담 : 2건 (분야별: 수련·근무 2, 생활·심리 2)
+합계 : 14건</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="95" customHeight="1" s="21">
       <c r="A14" s="17" t="inlineStr">

--- a/수련지도_입력양식_인턴.xlsx
+++ b/수련지도_입력양식_인턴.xlsx
@@ -182,7 +182,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -260,12 +260,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -690,8 +684,8 @@
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>총 5건
-· 임상 교육 4건: 인턴 역량평가·종합평가(소아청소년과 증례 설명·NICU 심초음파, 내과 기본 술기·외래 예진)
+          <t>총 3건
+· 임상 교육 2건: 소아청소년과 인턴 종합평가(회진 후 증례 설명, NICU 심초음파 교육)
 · 이론 교육 1건: 전체 인턴 교육(급성복통)</t>
         </is>
       </c>
@@ -728,7 +722,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1" s="21">
+    <row r="5" ht="24" customHeight="1" s="21">
       <c r="A5" s="23" t="n"/>
       <c r="B5" s="7" t="n">
         <v>4</v>
@@ -740,7 +734,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>총 28건 (분야: 수련·근무 27, 학습·역량 11, 진로·진학 23, 생활·심리 18, 분야 미기재 1)</t>
+          <t>총 3건 (분야: 수련·근무 3, 학습·역량 1, 진로·진학 3, 생활·심리 1)</t>
         </is>
       </c>
     </row>
@@ -760,7 +754,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="125" customHeight="1" s="21">
+    <row r="7" ht="74" customHeight="1" s="21">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>’26.8월</t>
@@ -776,10 +770,10 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>총 26건
-· 현장 교육 13건: 산부인과 병동·수술·외래 예진, 정형외과 수술방 scrub·부목 적용, 성형외과 수술실 마취 전 평가·환자안전, 응급실 bedside teaching·기본 술기, 신경외과 월간 수련지도(취합)
-· 임상 교육 6건: 내과·외과 인턴 역량평가(기본 술기, 외래 예진, 상급자 보고)
-· 이론 교육 7건: 전체 인턴 교육(의사과학자 양성 프로그램 소개), 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈, 이비인후과 외래 환자 응대</t>
+          <t>총 5건
+· 현장 교육 3건: 산부인과 병동 주치의·수술·외래 예진 지도
+· 임상 교육 1건: 소아청소년과 인턴 종합평가
+· 이론 교육 1건: 전체 인턴 교육(의사과학자 양성 프로그램 소개)</t>
         </is>
       </c>
     </row>
@@ -799,7 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1" s="21">
+    <row r="9" ht="24" customHeight="1" s="21">
       <c r="A9" s="23" t="n"/>
       <c r="B9" s="7" t="n">
         <v>3</v>
@@ -811,11 +805,11 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>총 3건: 정기 간담회(여성 전공의 모성보호, 신규 인턴 근무시간 명확화), 말초성·중추성 어지럼증 감별(인턴별 2건)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1" s="21">
+          <t>총 1건: 정기 간담회: 여성 전공의 모성보호, 신규 인턴 근무시간 명확화</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" s="21">
       <c r="A10" s="23" t="n"/>
       <c r="B10" s="7" t="n">
         <v>4</v>
@@ -827,7 +821,7 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>총 30건 (분야: 수련·근무 26, 학습·역량 11, 진로·진학 28, 생활·심리 20)</t>
+          <t>총 5건 (분야: 수련·근무 5, 학습·역량 2, 진로·진학 5, 생활·심리 2)</t>
         </is>
       </c>
     </row>
@@ -847,7 +841,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="159" customHeight="1" s="21">
+    <row r="12" ht="91" customHeight="1" s="21">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>’26.9월</t>
@@ -863,10 +857,10 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>총 68건
-· 현장 교육 31건: 산부인과 수술실·병동, 정형외과 수술방 무균술·C-arm, 성형외과·마취 수술실 환자안전, 응급실 초진·신경학적 진찰, 이비인후과 외래, 신경외과 병동 회진 교육(20건)
-· 임상 교육 26건: 영상의학 판독·초음파 교육(복부 CT·MRI, 간·담도·췌장 등), 소아청소년과 인턴 종합평가, 내과·외과 인턴 역량평가
-· 이론 교육 11건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응, 이비인후과 외래 업무</t>
+          <t>총 12건
+· 현장 교육 3건: 산부인과 수술실(수술 준비)·병동 주치의 지도
+· 임상 교육 5건: 소아청소년과 인턴 종합평가
+· 이론 교육 4건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호)</t>
         </is>
       </c>
     </row>
@@ -898,11 +892,11 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>총 2건: 정기 간담회(냉장고 교체·여자 휴게실 환경개선, 환자경험평가, 12월 면접 응시자격), 이비인후과 인턴 9월 간담회</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1" s="21">
+          <t>총 1건: 정기 간담회: 냉장고 교체·여자 휴게실 환경개선, 환자경험평가, 12월 면접 응시자격</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="21">
       <c r="A15" s="23" t="n"/>
       <c r="B15" s="7" t="n">
         <v>4</v>
@@ -914,7 +908,7 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>총 31건 (분야: 수련·근무 30, 학습·역량 13, 진로·진학 28, 생활·심리 19)</t>
+          <t>총 5건 (분야: 수련·근무 5, 학습·역량 2, 진로·진학 5, 생활·심리 2)</t>
         </is>
       </c>
     </row>
@@ -950,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
@@ -1022,7 +1016,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="95" customHeight="1" s="21">
+    <row r="3" ht="133" customHeight="1" s="21">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>부책임 지도전문의</t>
@@ -1033,407 +1027,39 @@
           <t>나재윤</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>소아청소년과 인턴 7명(노하경, 박현석, 김유림, 김은성, 김우탁, 김현석, 이예닮)</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>소아청소년과 인턴 10명(노하경, 박현석, 조융, 김정환, 정유진, 김유림, 김은성, 김우탁, 김현석, 이예닮)</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>7월 수련지도 : 2건 (임상 교육 2)
 7월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1, 생활·심리 1)
+8월 수련지도 : 1건 (임상 교육 1)
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
 9월 수련지도 : 8건 (임상 교육 5, 이론 교육 3)
 9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-합계 : 13건</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="114" customHeight="1" s="21">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>정수</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>이여진, 조유민, 조정욱, 김현석, 조융, 권도균</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E4" s="27" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-8월 수련지도 : 1건 (이론 교육 1)
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-9월 수련지도 : 1건 (이론 교육 1)
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-합계 : 8건</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="95" customHeight="1" s="21">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>유경헌</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>이승주, 전시형, 노하경, 임창열</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E5" s="27" t="inlineStr">
-        <is>
-          <t>8월 수련지도 : 2건 (현장 교육 2)
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-9월 수련지도 : 2건 (현장 교육 2)
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-합계 : 8건</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="114" customHeight="1" s="21">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>윤초석</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>김현진, 박서연, 이단비, 권도균, 손지형, 김준섭, 김준영, 김영은, 김지유</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E6" s="27" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-8월 수련지도 : 3건 (이론 교육 3)
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-9월 수련지도 : 3건 (이론 교육 3)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-합계 : 15건</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="133" customHeight="1" s="21">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>박진선</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>이은열, 조정욱, 노하경, 장연호, 최고은, 황의영, 이승연, 박준현</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t>7월 수련지도 : 2건 (임상 교육 2)
-7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2, 생활·심리 2)
-8월 수련지도 : 3건 (임상 교육 3)
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
-9월 수련지도 : 3건 (임상 교육 3)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
 합계 : 16건</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="133" customHeight="1" s="21">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>박신정</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>이예닮, 조융, 조윤지, 신동근, 조한얼, 이충환, 배정민, 설평안, 유병우, 인턴 전체(9월 인턴 교육)</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2, 분야 미기재 1)
-8월 수련지도 : 3건 (임상 교육 3)
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-9월 수련지도 : 4건 (임상 교육 3, 이론 교육 1)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-합계 : 16건</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="76" customHeight="1" s="21">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>윤성구</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>김수환, 김유림, 이종현, 조윤지, 권희정, 장호세</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 1, 진로·진학 3, 생활·심리 2)
-8월 개별 면담 : 3건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 3, 생활·심리 2)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 1)
-합계 : 9건</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="114" customHeight="1" s="21">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>김지윤</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>정해수, 전시형, 민현지, 이은열, 유은정, 이단비, 남혜원, 박수진, 김은수</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 1, 진로·진학 2)
-8월 수련지도 : 3건 (현장 교육 3)
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 2)
-9월 수련지도 : 3건 (현장 교육 3)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3)
-합계 : 14건</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="114" customHeight="1" s="21">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>홍승우</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>정문영, 최정민, 유채현, 전시형</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
-8월 수련지도 : 1건 (현장 교육 1)
-8월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
-9월 수련지도 : 20건 (현장 교육 20)
-9월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1, 생활·심리 1)
-합계 : 24건</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="114" customHeight="1" s="21">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>배근형</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>신동근, 이종현, 이종원, 박진서, 황규선</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1)
-8월 수련지도 : 2건 (현장 교육 2)
-8월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
-9월 수련지도 : 2건 (현장 교육 2)
-9월 개별 면담 : 2건 (분야별: 수련·근무 1, 진로·진학 2)
-합계 : 8건</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="152" customHeight="1" s="21">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>한상윤</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>이원우, 박승민, 정현도, 이예닮, 민현지, 김현진, 9월 간담회 참여 인턴</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1, 생활·심리 2)
-8월 수련지도 : 2건 (이론 교육 2)
-8월 간담회 : 2건
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1, 생활·심리 1)
-9월 수련지도 : 3건 (현장 교육 1, 이론 교육 2)
-9월 간담회 : 1건
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 생활·심리 2)
-합계 : 14건</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="95" customHeight="1" s="21">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>김미미</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>김현석, 이충환, 최정민, 김환우, 하기철, 신동근 외 1명(대상 미기재)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3)
-8월 개별 면담 : 2건 (분야별: 진로·진학 2)
-9월 수련지도 : 15건 (임상 교육 15)
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1)
-합계 : 22건</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="76" customHeight="1" s="21">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>교육전담</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>이준철</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>유은정, 이민재, 조유민, 강혜민 외 1명(대상 미기재)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>26.07.01~</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="inlineStr">
-        <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
-8월 수련지도 : 2건 (현장 교육 2)
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2, 생활·심리 2)
-합계 : 7건</t>
-        </is>
-      </c>
-    </row>
+    <row r="4" ht="19.5" customHeight="1" s="21"/>
+    <row r="5" ht="18" customHeight="1" s="21"/>
+    <row r="6" ht="18" customHeight="1" s="21"/>
+    <row r="7" ht="19.5" customHeight="1" s="21"/>
+    <row r="8" ht="19.5" customHeight="1" s="21"/>
+    <row r="9" ht="19.5" customHeight="1" s="21"/>
+    <row r="10" ht="19.5" customHeight="1" s="21"/>
+    <row r="11" ht="19.5" customHeight="1" s="21"/>
+    <row r="12" ht="19.5" customHeight="1" s="21"/>
+    <row r="13" ht="19.5" customHeight="1" s="21"/>
+    <row r="14" ht="19.5" customHeight="1" s="21"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/수련지도_입력양식_인턴.xlsx
+++ b/수련지도_입력양식_인턴.xlsx
@@ -722,7 +722,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="21">
+    <row r="5" ht="40" customHeight="1" s="21">
       <c r="A5" s="23" t="n"/>
       <c r="B5" s="7" t="n">
         <v>4</v>
@@ -734,7 +734,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>총 3건 (분야: 수련·근무 3, 학습·역량 1, 진로·진학 3, 생활·심리 1)</t>
+          <t>총 14건 (분야: 수련·근무 14, 학습·역량 6, 진로·진학 13, 생활·심리 12)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="74" customHeight="1" s="21">
+    <row r="7" ht="108" customHeight="1" s="21">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>’26.8월</t>
@@ -770,10 +770,10 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>총 5건
-· 현장 교육 3건: 산부인과 병동 주치의·수술·외래 예진 지도
+          <t>총 15건
+· 현장 교육 7건: 산부인과 병동 주치의·수술·외래 예진, 응급실 기본 술기, 이비인후과 외래, 신경외과 월간 수련지도(취합)
 · 임상 교육 1건: 소아청소년과 인턴 종합평가
-· 이론 교육 1건: 전체 인턴 교육(의사과학자 양성 프로그램 소개)</t>
+· 이론 교육 7건: 전체 인턴 교육(의사과학자 양성 프로그램 소개), 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈, 이비인후과 외래 환자 응대</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" s="21">
+    <row r="9" ht="40" customHeight="1" s="21">
       <c r="A9" s="23" t="n"/>
       <c r="B9" s="7" t="n">
         <v>3</v>
@@ -805,11 +805,11 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>총 1건: 정기 간담회: 여성 전공의 모성보호, 신규 인턴 근무시간 명확화</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" s="21">
+          <t>총 3건: 정기 간담회(여성 전공의 모성보호, 신규 인턴 근무시간 명확화), 말초성·중추성 어지럼증 감별(인턴별 2건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1" s="21">
       <c r="A10" s="23" t="n"/>
       <c r="B10" s="7" t="n">
         <v>4</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>총 5건 (분야: 수련·근무 5, 학습·역량 2, 진로·진학 5, 생활·심리 2)</t>
+          <t>총 15건 (분야: 수련·근무 15, 학습·역량 7, 진로·진학 14, 생활·심리 11)</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="91" customHeight="1" s="21">
+    <row r="12" ht="125" customHeight="1" s="21">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>’26.9월</t>
@@ -857,10 +857,10 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>총 12건
-· 현장 교육 3건: 산부인과 수술실(수술 준비)·병동 주치의 지도
+          <t>총 46건
+· 현장 교육 31건: 산부인과 수술실·병동, 신경외과 병동 회진 교육(20건), 이비인후과 외래·수술실, 응급실 수련지도
 · 임상 교육 5건: 소아청소년과 인턴 종합평가
-· 이론 교육 4건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호)</t>
+· 이론 교육 10건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응, 이비인후과 외래 업무</t>
         </is>
       </c>
     </row>
@@ -892,11 +892,11 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>총 1건: 정기 간담회: 냉장고 교체·여자 휴게실 환경개선, 환자경험평가, 12월 면접 응시자격</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" s="21">
+          <t>총 2건: 정기 간담회(냉장고 교체·여자 휴게실 환경개선, 환자경험평가, 12월 면접 응시자격), 이비인후과 인턴 9월 간담회</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1" s="21">
       <c r="A15" s="23" t="n"/>
       <c r="B15" s="7" t="n">
         <v>4</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>총 5건 (분야: 수련·근무 5, 학습·역량 2, 진로·진학 5, 생활·심리 2)</t>
+          <t>총 15건 (분야: 수련·근무 15, 학습·역량 10, 진로·진학 13, 생활·심리 10)</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
@@ -1049,11 +1049,168 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="19.5" customHeight="1" s="21"/>
-    <row r="5" ht="18" customHeight="1" s="21"/>
-    <row r="6" ht="18" customHeight="1" s="21"/>
-    <row r="7" ht="19.5" customHeight="1" s="21"/>
-    <row r="8" ht="19.5" customHeight="1" s="21"/>
+    <row r="4" ht="114" customHeight="1" s="21">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>이여진, 조유민, 조정욱, 김현석, 조융, 권도균</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+8월 수련지도 : 1건 (이론 교육 1)
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+9월 수련지도 : 1건 (이론 교육 1)
+9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+합계 : 8건</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="152" customHeight="1" s="21">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>한상윤</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>이원우, 박승민, 정현도, 이예닮, 민현지, 김현진, 9월 간담회 참여 인턴</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1, 생활·심리 2)
+8월 수련지도 : 3건 (현장 교육 1, 이론 교육 2)
+8월 간담회 : 2건
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1, 생활·심리 1)
+9월 수련지도 : 8건 (현장 교육 6, 이론 교육 2)
+9월 간담회 : 1건
+9월 개별 면담 : 2건 (분야별: 수련·근무 2, 생활·심리 2)
+합계 : 20건</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="114" customHeight="1" s="21">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>홍승우</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>정문영, 최정민, 유채현, 전시형</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
+8월 수련지도 : 1건 (현장 교육 1)
+8월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
+9월 수련지도 : 20건 (현장 교육 20)
+9월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1, 생활·심리 1)
+합계 : 24건</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="114" customHeight="1" s="21">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>이준철</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>유은정, 이민재, 조유민, 강혜민, 김상엽, 김형윤 외 1명(대상 미기재)</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
+8월 수련지도 : 2건 (현장 교육 2)
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2, 생활·심리 2)
+9월 수련지도 : 2건 (현장 교육 2)
+9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2)
+합계 : 11건</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="114" customHeight="1" s="21">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>윤초석</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>김현진, 박서연, 이단비, 권도균, 손지형, 김준섭, 김준영, 김영은, 김지유</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
+8월 수련지도 : 3건 (이론 교육 3)
+8월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
+9월 수련지도 : 3건 (이론 교육 3)
+9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
+합계 : 15건</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="19.5" customHeight="1" s="21"/>
     <row r="10" ht="19.5" customHeight="1" s="21"/>
     <row r="11" ht="19.5" customHeight="1" s="21"/>

--- a/수련지도_입력양식_인턴.xlsx
+++ b/수련지도_입력양식_인턴.xlsx
@@ -684,8 +684,8 @@
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>총 3건
-· 임상 교육 2건: 소아청소년과 인턴 종합평가(회진 후 증례 설명, NICU 심초음파 교육)
+          <t>총 5건
+· 임상 교육 4건: 인턴 종합평가·역량평가(소아청소년과 증례 설명·NICU 심초음파, 내과 기본 술기·외래 예진)
 · 이론 교육 1건: 전체 인턴 교육(급성복통)</t>
         </is>
       </c>
@@ -734,7 +734,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>총 14건 (분야: 수련·근무 14, 학습·역량 6, 진로·진학 13, 생활·심리 12)</t>
+          <t>총 24건 (분야: 수련·근무 23, 학습·역량 9, 진로·진학 19, 생활·심리 16, 분야 미기재 1)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="108" customHeight="1" s="21">
+    <row r="7" ht="125" customHeight="1" s="21">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>’26.8월</t>
@@ -770,9 +770,9 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>총 15건
-· 현장 교육 7건: 산부인과 병동 주치의·수술·외래 예진, 응급실 기본 술기, 이비인후과 외래, 신경외과 월간 수련지도(취합)
-· 임상 교육 1건: 소아청소년과 인턴 종합평가
+          <t>총 24건
+· 현장 교육 10건: 산부인과 병동 주치의·수술·외래 예진, 응급실 기본 술기, 이비인후과 외래, 성형외과·마취 수술실, 신경외과 월간 수련지도(취합)
+· 임상 교육 7건: 인턴 종합평가·역량평가(소아청소년과, 내과·외과 기본 술기·외래 예진·상급자 보고)
 · 이론 교육 7건: 전체 인턴 교육(의사과학자 양성 프로그램 소개), 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈, 이비인후과 외래 환자 응대</t>
         </is>
       </c>
@@ -821,7 +821,7 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>총 15건 (분야: 수련·근무 15, 학습·역량 7, 진로·진학 14, 생활·심리 11)</t>
+          <t>총 26건 (분야: 수련·근무 24, 학습·역량 10, 진로·진학 24, 생활·심리 17)</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="125" customHeight="1" s="21">
+    <row r="12" ht="142" customHeight="1" s="21">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>’26.9월</t>
@@ -857,10 +857,10 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>총 46건
-· 현장 교육 31건: 산부인과 수술실·병동, 신경외과 병동 회진 교육(20건), 이비인후과 외래·수술실, 응급실 수련지도
-· 임상 교육 5건: 소아청소년과 인턴 종합평가
-· 이론 교육 10건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응, 이비인후과 외래 업무</t>
+          <t>총 72건
+· 현장 교육 35건: 산부인과 수술실·병동, 신경외과 병동 회진 교육(20건), 이비인후과 외래·수술실, 성형외과·마취 수술실, 응급실 수련지도
+· 임상 교육 26건: 영상의학 판독·초음파 교육(복부 CT·MRI, 간·담도·췌장 등), 인턴 종합평가·역량평가(소아청소년과, 내과·외과)
+· 이론 교육 11건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응, 이비인후과 외래 업무</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>총 15건 (분야: 수련·근무 15, 학습·역량 10, 진로·진학 13, 생활·심리 10)</t>
+          <t>총 26건 (분야: 수련·근무 26, 학습·역량 13, 진로·진학 23, 생활·심리 16)</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
@@ -1211,10 +1211,134 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1" s="21"/>
-    <row r="10" ht="19.5" customHeight="1" s="21"/>
-    <row r="11" ht="19.5" customHeight="1" s="21"/>
-    <row r="12" ht="19.5" customHeight="1" s="21"/>
+    <row r="9" ht="133" customHeight="1" s="21">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>박신정</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>이예닮, 조융, 조윤지, 신동근, 조한얼, 이충환, 배정민, 설평안, 유병우, 인턴 전체(9월 인턴 교육)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2, 분야 미기재 1)
+8월 수련지도 : 3건 (임상 교육 3)
+8월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
+9월 수련지도 : 4건 (임상 교육 3, 이론 교육 1)
+9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
+합계 : 16건</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="133" customHeight="1" s="21">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>박진선</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>이은열, 조정욱, 노하경, 장연호, 최고은, 황의영, 이승연, 박준현</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>7월 수련지도 : 2건 (임상 교육 2)
+7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2, 생활·심리 2)
+8월 수련지도 : 3건 (임상 교육 3)
+8월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
+9월 수련지도 : 3건 (임상 교육 3)
+9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
+합계 : 16건</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="95" customHeight="1" s="21">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>김미미</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>김현석, 이충환, 최정민, 김환우, 하기철, 신동근 외 1명(대상 미기재)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3)
+8월 개별 면담 : 2건 (분야별: 진로·진학 2)
+9월 수련지도 : 15건 (임상 교육 15)
+9월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1)
+합계 : 22건</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="114" customHeight="1" s="21">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>김지윤</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>정해수, 전시형, 민현지, 이은열, 유은정, 이단비, 남혜원, 박수진, 김은수</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 1, 진로·진학 2)
+8월 수련지도 : 3건 (현장 교육 3)
+8월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 2)
+9월 수련지도 : 4건 (현장 교육 4)
+9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3)
+합계 : 15건</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="19.5" customHeight="1" s="21"/>
     <row r="14" ht="19.5" customHeight="1" s="21"/>
   </sheetData>

--- a/수련지도_입력양식_인턴.xlsx
+++ b/수련지도_입력양식_인턴.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>총 24건 (분야: 수련·근무 23, 학습·역량 9, 진로·진학 19, 생활·심리 16, 분야 미기재 1)</t>
+          <t>총 28건 (분야: 수련·근무 27, 학습·역량 11, 진로·진학 23, 생활·심리 18, 분야 미기재 1)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="125" customHeight="1" s="21">
+    <row r="7" ht="142" customHeight="1" s="21">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>’26.8월</t>
@@ -770,8 +770,8 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>총 24건
-· 현장 교육 10건: 산부인과 병동 주치의·수술·외래 예진, 응급실 기본 술기, 이비인후과 외래, 성형외과·마취 수술실, 신경외과 월간 수련지도(취합)
+          <t>총 28건
+· 현장 교육 14건: 산부인과 병동 주치의·수술·외래 예진, 응급실 bedside teaching·기본 술기, 정형외과 수술방 scrub·부목, 이비인후과 외래, 성형외과·마취 수술실, 신경외과 월간 수련지도(취합)
 · 임상 교육 7건: 인턴 종합평가·역량평가(소아청소년과, 내과·외과 기본 술기·외래 예진·상급자 보고)
 · 이론 교육 7건: 전체 인턴 교육(의사과학자 양성 프로그램 소개), 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈, 이비인후과 외래 환자 응대</t>
         </is>
@@ -821,7 +821,7 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>총 26건 (분야: 수련·근무 24, 학습·역량 10, 진로·진학 24, 생활·심리 17)</t>
+          <t>총 32건 (분야: 수련·근무 28, 학습·역량 13, 진로·진학 30, 생활·심리 22)</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="142" customHeight="1" s="21">
+    <row r="12" ht="159" customHeight="1" s="21">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>’26.9월</t>
@@ -857,8 +857,8 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>총 72건
-· 현장 교육 35건: 산부인과 수술실·병동, 신경외과 병동 회진 교육(20건), 이비인후과 외래·수술실, 성형외과·마취 수술실, 응급실 수련지도
+          <t>총 76건
+· 현장 교육 39건: 산부인과 수술실·병동, 신경외과 병동 회진 교육(20건), 이비인후과 외래·수술실, 성형외과·마취 수술실, 정형외과 수술방 무균술·C-arm, 응급실 초진·신경학적 진찰
 · 임상 교육 26건: 영상의학 판독·초음파 교육(복부 CT·MRI, 간·담도·췌장 등), 인턴 종합평가·역량평가(소아청소년과, 내과·외과)
 · 이론 교육 11건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응, 이비인후과 외래 업무</t>
         </is>
@@ -908,7 +908,7 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>총 26건 (분야: 수련·근무 26, 학습·역량 13, 진로·진학 23, 생활·심리 16)</t>
+          <t>총 33건 (분야: 수련·근무 32, 학습·역량 15, 진로·진학 30, 생활·심리 19)</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
@@ -1339,8 +1339,99 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1" s="21"/>
-    <row r="14" ht="19.5" customHeight="1" s="21"/>
+    <row r="13" ht="76" customHeight="1" s="21">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>윤성구</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>김수환, 김유림, 이종현, 조윤지, 권희정, 장호세</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 1, 진로·진학 3, 생활·심리 2)
+8월 개별 면담 : 3건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 3, 생활·심리 2)
+9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 1)
+합계 : 9건</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="114" customHeight="1" s="21">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>배근형</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>신동근, 이종현, 이종원, 박진서, 황규선</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>7월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1)
+8월 수련지도 : 2건 (현장 교육 2)
+8월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
+9월 수련지도 : 2건 (현장 교육 2)
+9월 개별 면담 : 2건 (분야별: 수련·근무 1, 진로·진학 2)
+합계 : 8건</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="95" customHeight="1" s="21">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>유경헌</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>이승주, 전시형, 노하경, 임창열</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>8월 수련지도 : 2건 (현장 교육 2)
+8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+9월 수련지도 : 2건 (현장 교육 2)
+9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
+합계 : 8건</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/수련지도_입력양식_인턴.xlsx
+++ b/수련지도_입력양식_인턴.xlsx
@@ -668,7 +668,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="74" customHeight="1" s="21">
+    <row r="2" ht="57" customHeight="1" s="21">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>’26.7월</t>
@@ -684,9 +684,8 @@
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>총 5건
-· 임상 교육 4건: 인턴 종합평가·역량평가(소아청소년과 증례 설명·NICU 심초음파, 내과 기본 술기·외래 예진)
-· 이론 교육 1건: 전체 인턴 교육(급성복통)</t>
+          <t>총 4건
+· 임상 교육 4건: 인턴 종합평가·역량평가(소아청소년과 증례 설명·NICU 심초음파, 내과 기본 술기·외래 예진)</t>
         </is>
       </c>
     </row>
@@ -697,12 +696,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>학술집담회</t>
+          <t>인턴교육</t>
         </is>
       </c>
       <c r="D3" s="22" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>총 1건: 전체 인턴 교육(급성복통, 외과 박성실 교수 강의)</t>
         </is>
       </c>
     </row>
@@ -770,10 +769,10 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>총 28건
+          <t>총 27건
 · 현장 교육 14건: 산부인과 병동 주치의·수술·외래 예진, 응급실 bedside teaching·기본 술기, 정형외과 수술방 scrub·부목, 이비인후과 외래, 성형외과·마취 수술실, 신경외과 월간 수련지도(취합)
 · 임상 교육 7건: 인턴 종합평가·역량평가(소아청소년과, 내과·외과 기본 술기·외래 예진·상급자 보고)
-· 이론 교육 7건: 전체 인턴 교육(의사과학자 양성 프로그램 소개), 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈, 이비인후과 외래 환자 응대</t>
+· 이론 교육 6건: 급성기 뇌경색 workflow, 감염내과 환자 특성·혈액배양 채혈, 이비인후과 외래 환자 응대</t>
         </is>
       </c>
     </row>
@@ -784,12 +783,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>학술집담회</t>
+          <t>인턴교육</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>총 1건: 전체 인턴 교육(의사과학자 양성 프로그램 소개, 신경과 김영서 교수 강의)</t>
         </is>
       </c>
     </row>
@@ -841,7 +840,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="159" customHeight="1" s="21">
+    <row r="12" ht="142" customHeight="1" s="21">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>’26.9월</t>
@@ -857,26 +856,26 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>총 76건
+          <t>총 71건
 · 현장 교육 39건: 산부인과 수술실·병동, 신경외과 병동 회진 교육(20건), 이비인후과 외래·수술실, 성형외과·마취 수술실, 정형외과 수술방 무균술·C-arm, 응급실 초진·신경학적 진찰
 · 임상 교육 26건: 영상의학 판독·초음파 교육(복부 CT·MRI, 간·담도·췌장 등), 인턴 종합평가·역량평가(소아청소년과, 내과·외과)
-· 이론 교육 11건: 소아청소년과 분과 강의(식품알레르기·신생아 황달·소아 내분비), 전체 인턴 교육(외과 수술 후 주의 신호), Lateral medullary infarction, 내과 환자 급성기 대응, 이비인후과 외래 업무</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" s="21">
+· 이론 교육 6건: Lateral medullary infarction, 내과 환자 급성기 대응, 이비인후과 외래 업무</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="57" customHeight="1" s="21">
       <c r="A13" s="23" t="n"/>
       <c r="B13" s="7" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>학술집담회</t>
+          <t>인턴교육</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>총 5건: 전체 인턴 교육(외과 수술 후 놓치면 안 되는 신호) 2건(주관 이원무·강사 박신정 각각 등록), 소아청소년과 분과 전문의 인턴교육 3건(식품알레르기·신생아 황달·소아 내분비)</t>
         </is>
       </c>
     </row>
@@ -980,7 +979,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="190" customHeight="1" s="21">
+    <row r="2" ht="228" customHeight="1" s="21">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>책임 지도전문의</t>
@@ -1003,20 +1002,22 @@
       </c>
       <c r="E2" s="26" t="inlineStr">
         <is>
-          <t>7월 수련지도 : 1건 (이론 교육 1)
+          <t>7월 인턴교육 : 1건
 7월 간담회 : 1건
 7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2)
-8월 수련지도 : 4건 (현장 교육 3, 이론 교육 1)
+8월 수련지도 : 3건 (현장 교육 3)
+8월 인턴교육 : 1건
 8월 간담회 : 1건
 8월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3)
-9월 수련지도 : 4건 (현장 교육 3, 이론 교육 1)
+9월 수련지도 : 3건 (현장 교육 3)
+9월 인턴교육 : 1건
 9월 간담회 : 1건
 9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3)
 합계 : 20건</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="133" customHeight="1" s="21">
+    <row r="3" ht="152" customHeight="1" s="21">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>부책임 지도전문의</t>
@@ -1043,7 +1044,8 @@
 7월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1, 생활·심리 1)
 8월 수련지도 : 1건 (임상 교육 1)
 8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-9월 수련지도 : 8건 (임상 교육 5, 이론 교육 3)
+9월 수련지도 : 5건 (임상 교육 5)
+9월 인턴교육 : 3건
 9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
 합계 : 16건</t>
         </is>
@@ -1211,7 +1213,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="133" customHeight="1" s="21">
+    <row r="9" ht="152" customHeight="1" s="21">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1237,7 +1239,8 @@
           <t>7월 개별 면담 : 3건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2, 분야 미기재 1)
 8월 수련지도 : 3건 (임상 교육 3)
 8월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-9월 수련지도 : 4건 (임상 교육 3, 이론 교육 1)
+9월 수련지도 : 3건 (임상 교육 3)
+9월 인턴교육 : 1건
 9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
 합계 : 16건</t>
         </is>

--- a/수련지도_입력양식_인턴.xlsx
+++ b/수련지도_입력양식_인턴.xlsx
@@ -260,7 +260,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -947,9 +947,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
-    <col width="30" customWidth="1" style="21" min="3" max="3"/>
+    <col width="16" customWidth="1" style="21" min="3" max="3"/>
     <col width="20.75" customWidth="1" style="21" min="4" max="4"/>
-    <col width="80" customWidth="1" style="21" min="5" max="5"/>
+    <col width="75" customWidth="1" style="21" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="21">
@@ -979,7 +979,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="228" customHeight="1" s="21">
+    <row r="2" ht="193" customHeight="1" s="21">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>책임 지도전문의</t>
@@ -992,7 +992,14 @@
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>산부인과 인턴 8명(이충환, 조중현, 김소윤, 황규선, 김태인, 백승헌, 조은시, 장현복), 서울병원 근무 인턴 전체(인턴 교육·간담회)</t>
+          <t>조중현
+이충환
+김태인
+김소윤
+황규선
+백승헌
+장현복
+조은시</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
@@ -1002,22 +1009,21 @@
       </c>
       <c r="E2" s="26" t="inlineStr">
         <is>
-          <t>7월 인턴교육 : 1건
-7월 간담회 : 1건
-7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2)
-8월 수련지도 : 3건 (현장 교육 3)
-8월 인턴교육 : 1건
-8월 간담회 : 1건
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3)
-9월 수련지도 : 3건 (현장 교육 3)
-9월 인턴교육 : 1건
-9월 간담회 : 1건
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3)
-합계 : 20건</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="152" customHeight="1" s="21">
+          <t>7월 인턴교육(권도균 외 15명)
+7월 간담회(권도균 외 15명)
+7월 면담 : 진로상담(조중현, 이충환)
+8월 인턴교육(권도균 외 19명)
+8월 간담회(권도균 외 18명)
+8월 면담 : 진로상담(황규선, 김태인, 김소윤)
+8월 수련지도 : 부인과 질환, 수술지도(황규선, 김태인, 김소윤)
+9월 인턴교육(권도균 외 41명)
+9월 간담회(권도균 외 29명)
+9월 면담 : 진로상담(백승헌, 장현복, 조은시)
+9월 수련지도 : 병동 현장 지도(백승헌, 장현복, 조은시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="159" customHeight="1" s="21">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>부책임 지도전문의</t>
@@ -1030,7 +1036,15 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>소아청소년과 인턴 10명(노하경, 박현석, 조융, 김정환, 정유진, 김유림, 김은성, 김우탁, 김현석, 이예닮)</t>
+          <t>노하경
+박현석
+정유진
+김정환
+김유림
+김은성
+이예닮
+김우탁
+김현석</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1040,18 +1054,17 @@
       </c>
       <c r="E3" s="26" t="inlineStr">
         <is>
-          <t>7월 수련지도 : 2건 (임상 교육 2)
-7월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1, 생활·심리 1)
-8월 수련지도 : 1건 (임상 교육 1)
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-9월 수련지도 : 5건 (임상 교육 5)
-9월 인턴교육 : 3건
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-합계 : 16건</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="114" customHeight="1" s="21">
+          <t>7월 면담 : 수련 고충·진로상담(노하경, 박현석)
+7월 수련지도 : 인턴 종합평가(병동·NICU 지도)(노하경, 박현석)
+8월 면담 : 수련 고충·진로상담(노하경, 박현석, 정유진)
+8월 수련지도 : 인턴 종합평가(병동 지도)(김정환)
+9월 인턴교육 : 소아청소년과 분과 강의(김우탁, 김유림, 김은성, 김현석, 이예닮)
+9월 면담 : 수련 고충·진로상담(김유림, 김은성, 이예닮, 김우탁, 김현석)
+9월 수련지도 : 인턴 종합평가(병동·외래 지도)(이예닮, 김현석, 김은성, 김우탁, 김유림)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="108" customHeight="1" s="21">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1064,7 +1077,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>이여진, 조유민, 조정욱, 김현석, 조융, 권도균</t>
+          <t>이여진
+조유민
+조정욱
+김현석
+조융
+권도균</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -1074,16 +1092,15 @@
       </c>
       <c r="E4" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-8월 수련지도 : 1건 (이론 교육 1)
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-9월 수련지도 : 1건 (이론 교육 1)
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-합계 : 8건</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="152" customHeight="1" s="21">
+          <t>7월 면담 : 수련 피드백·진로상담(이여진, 조유민)
+8월 면담 : 수련 피드백·진로상담(조정욱, 김현석)
+8월 수련지도 : 급성기 뇌경색 Workflow 교육(김현석, 조정욱)
+9월 면담 : 수련 피드백·진로상담(조융, 권도균)
+9월 수련지도 : Lateral medullary infarction 교육(권도균, 조융)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="125" customHeight="1" s="21">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1096,7 +1113,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>이원우, 박승민, 정현도, 이예닮, 민현지, 김현진, 9월 간담회 참여 인턴</t>
+          <t>이원우
+박승민
+정현도
+이예닮
+민현지
+김현진</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1106,18 +1128,17 @@
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1, 생활·심리 2)
-8월 수련지도 : 3건 (현장 교육 1, 이론 교육 2)
-8월 간담회 : 2건
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1, 생활·심리 1)
-9월 수련지도 : 8건 (현장 교육 6, 이론 교육 2)
-9월 간담회 : 1건
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 생활·심리 2)
-합계 : 20건</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="114" customHeight="1" s="21">
+          <t>7월 면담 : 인턴 생활 고충·개선사항 상담(이원우, 박승민)
+8월 간담회 : 말초성·중추성 어지럼증 감별(이예닮, 정현도)
+8월 면담 : 인턴 생활 고충·개선사항 상담(정현도, 이예닮)
+8월 수련지도 : 외래 업무 지도(정현도, 이예닮)
+9월 간담회(간담회 참여 인턴)
+9월 면담 : 인턴 생활 고충·개선사항 상담(민현지, 김현진)
+9월 수련지도 : 외래·병동 진료 및 수술 준비 교육(김현진, 민현지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="91" customHeight="1" s="21">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1130,7 +1151,11 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>정문영, 최정민, 유채현, 전시형</t>
+          <t>정문영
+장연호
+최정민
+전시형
+유채현</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1140,16 +1165,15 @@
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
-8월 수련지도 : 1건 (현장 교육 1)
-8월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
-9월 수련지도 : 20건 (현장 교육 20)
-9월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1, 생활·심리 1)
-합계 : 24건</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="114" customHeight="1" s="21">
+          <t>7월 면담 : 진로 및 수련상태 공동면담(정문영, 장연호)
+8월 면담 : 진로 및 수련상태 공동면담(최정민, 정문영)
+8월 수련지도 : 신경외과 월간 수련지도(정문영, 최정민)
+9월 면담 : 진로 및 수련상태 공동면담(전시형, 유채현)
+9월 수련지도 : 신경외과 병동 회진 교육(유채현)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="108" customHeight="1" s="21">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1162,7 +1186,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>유은정, 이민재, 조유민, 강혜민, 김상엽, 김형윤 외 1명(대상 미기재)</t>
+          <t>유은정
+이민재
+조유민
+강혜민
+김형윤
+김상엽</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1172,16 +1201,15 @@
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
-8월 수련지도 : 2건 (현장 교육 2)
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2, 생활·심리 2)
-9월 수련지도 : 2건 (현장 교육 2)
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2)
-합계 : 11건</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="114" customHeight="1" s="21">
+          <t>7월 면담 : 수련 환경·고충 상담(유은정, 이민재)
+8월 면담 : 수련 환경·고충 상담(조유민, 강혜민)
+8월 수련지도 : 응급실 기본 술기 지도(조유민, 강혜민)
+9월 면담 : 수련 환경·고충 상담(김형윤, 김상엽)
+9월 수련지도 : 응급실 수련지도(김형윤, 김상엽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="159" customHeight="1" s="21">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1194,7 +1222,15 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>김현진, 박서연, 이단비, 권도균, 손지형, 김준섭, 김준영, 김영은, 김지유</t>
+          <t>김현진
+박서연
+이단비
+권도균
+손지형
+김준섭
+김준영
+김영은
+김지유</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -1204,16 +1240,15 @@
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-8월 수련지도 : 3건 (이론 교육 3)
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-9월 수련지도 : 3건 (이론 교육 3)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-합계 : 15건</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="152" customHeight="1" s="21">
+          <t>7월 면담 : 업무 부담·수련 고충 상담(김현진, 박서연, 이단비)
+8월 면담 : 업무 부담·수련 고충 상담(권도균, 손지형, 김준섭)
+8월 수련지도 : 감염내과 환자 특성·혈액배양 채혈 교육(김준섭, 권도균, 손지형)
+9월 면담 : 업무 부담·수련 고충 상담(김준영, 김영은, 김지유)
+9월 수련지도 : 내과 환자 급성기 대응·혈액배양 채혈 교육(김지유, 김준영, 김영은)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="159" customHeight="1" s="21">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1226,7 +1261,15 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>이예닮, 조융, 조윤지, 신동근, 조한얼, 이충환, 배정민, 설평안, 유병우, 인턴 전체(9월 인턴 교육)</t>
+          <t>이예닮
+조융
+조윤지
+신동근
+조한얼
+이충환
+배정민
+설평안
+유병우</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1236,17 +1279,16 @@
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2, 분야 미기재 1)
-8월 수련지도 : 3건 (임상 교육 3)
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-9월 수련지도 : 3건 (임상 교육 3)
-9월 인턴교육 : 1건
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 3, 진로·진학 3, 생활·심리 3)
-합계 : 16건</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="133" customHeight="1" s="21">
+          <t>7월 면담 : 수련 적응·진로상담(이예닮, 조융, 조윤지)
+8월 면담 : 수련 적응·진로상담(신동근, 조한얼, 이충환)
+8월 수련지도 : 외과 외래·병동 역량평가(신동근, 이충환, 조한얼)
+9월 인턴교육 : 외과 수술 후 놓치면 안 되는 신호(전시형 외 90명)
+9월 면담 : 수련 적응·진로상담(배정민, 설평안, 유병우)
+9월 수련지도 : 외과 병동·외래 역량평가(배정민, 설평안, 유병우)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="142" customHeight="1" s="21">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1259,7 +1301,14 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>이은열, 조정욱, 노하경, 장연호, 최고은, 황의영, 이승연, 박준현</t>
+          <t>이은열
+조정욱
+노하경
+장연호
+최고은
+황의영
+이승연
+박준현</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1269,17 +1318,16 @@
       </c>
       <c r="E10" s="26" t="inlineStr">
         <is>
-          <t>7월 수련지도 : 2건 (임상 교육 2)
-7월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 2, 생활·심리 2)
-8월 수련지도 : 3건 (임상 교육 3)
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
-9월 수련지도 : 3건 (임상 교육 3)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 3)
-합계 : 16건</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="95" customHeight="1" s="21">
+          <t>7월 면담 : 근무환경·애로사항 상담(이은열, 조정욱)
+7월 수련지도 : 기본 술기·외래 예진 역량평가(이은열, 조정욱)
+8월 면담 : 근무환경·애로사항 상담(노하경, 장연호, 최고은)
+8월 수련지도 : 기본 술기·외래 예진 역량평가(노하경, 장연호, 최고은)
+9월 면담 : 근무환경·애로사항 상담(황의영, 이승연, 박준현)
+9월 수련지도 : 기본 술기·외래 예진 역량평가(박준현, 이승연, 황의영)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="108" customHeight="1" s="21">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1292,7 +1340,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>김현석, 이충환, 최정민, 김환우, 하기철, 신동근 외 1명(대상 미기재)</t>
+          <t>김현석
+이충환
+최정민
+김환우
+하기철
+신동근</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1302,15 +1355,14 @@
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3)
-8월 개별 면담 : 2건 (분야별: 진로·진학 2)
-9월 수련지도 : 15건 (임상 교육 15)
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 진로·진학 1)
-합계 : 22건</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="114" customHeight="1" s="21">
+          <t>7월 면담 : 수련 상담(김현석, 이충환, 최정민)
+8월 면담 : 진로상담(김환우)
+9월 면담 : 수련·진로상담(하기철, 신동근)
+9월 수련지도 : 영상의학 판독·초음파 교육(하기철, 신동근)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="159" customHeight="1" s="21">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1323,7 +1375,15 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>정해수, 전시형, 민현지, 이은열, 유은정, 이단비, 남혜원, 박수진, 김은수</t>
+          <t>정해수
+전시형
+민현지
+이은열
+유은정
+이단비
+김은수
+박수진
+남혜원</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1333,16 +1393,15 @@
       </c>
       <c r="E12" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 1, 진로·진학 2)
-8월 수련지도 : 3건 (현장 교육 3)
-8월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 2)
-9월 수련지도 : 4건 (현장 교육 4)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3)
-합계 : 15건</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="76" customHeight="1" s="21">
+          <t>7월 면담 : 수련·진로상담(정해수, 전시형, 민현지)
+8월 면담 : 수련·진로상담(이은열, 유은정, 이단비)
+8월 수련지도 : 성형외과·마취 수술실 지도(이은열, 유은정, 이단비)
+9월 면담 : 수련·진로상담(김은수, 박수진, 남혜원)
+9월 수련지도 : 성형외과·마취 수술실 지도(김은수, 남혜원, 박수진)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="108" customHeight="1" s="21">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1355,7 +1414,12 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>김수환, 김유림, 이종현, 조윤지, 권희정, 장호세</t>
+          <t>김수환
+김유림
+이종현
+조윤지
+권희정
+장호세</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1365,14 +1429,13 @@
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 1, 진로·진학 3, 생활·심리 2)
-8월 개별 면담 : 3건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 3, 생활·심리 2)
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 진로·진학 3, 생활·심리 1)
-합계 : 9건</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="114" customHeight="1" s="21">
+          <t>7월 면담 : 수련 및 진로 상담(김수환, 김유림, 이종현)
+8월 면담 : 수련 및 진로 상담(김유림, 김수환, 조윤지)
+9월 면담 : 수련 및 진로 상담(권희정, 조윤지, 장호세)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="91" customHeight="1" s="21">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1385,7 +1448,11 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>신동근, 이종현, 이종원, 박진서, 황규선</t>
+          <t>신동근
+이종현
+이종원
+박진서
+황규선</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1395,16 +1462,15 @@
       </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
-          <t>7월 개별 면담 : 1건 (분야별: 수련·근무 1, 학습·역량 1, 진로·진학 1)
-8월 수련지도 : 2건 (현장 교육 2)
-8월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1, 생활·심리 1)
-9월 수련지도 : 2건 (현장 교육 2)
-9월 개별 면담 : 2건 (분야별: 수련·근무 1, 진로·진학 2)
-합계 : 8건</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="95" customHeight="1" s="21">
+          <t>7월 면담 : 인턴 업무·진로상담(신동근)
+8월 면담 : 인턴 업무·진로상담(이종현, 이종원)
+8월 수련지도 : 정형외과 수술방 scrub·부목 교육(이종원, 이종현)
+9월 면담 : 인턴 업무·진로상담(박진서, 황규선)
+9월 수련지도 : 수술방 무균술·C-arm 교육(황규선, 박진서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="74" customHeight="1" s="21">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1417,7 +1483,10 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>이승주, 전시형, 노하경, 임창열</t>
+          <t>이승주
+전시형
+임창열
+노하경</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1427,11 +1496,10 @@
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>8월 수련지도 : 2건 (현장 교육 2)
-8월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-9월 수련지도 : 2건 (현장 교육 2)
-9월 개별 면담 : 2건 (분야별: 수련·근무 2, 학습·역량 2, 진로·진학 2, 생활·심리 2)
-합계 : 8건</t>
+          <t>8월 면담 : 수련·진로상담(이승주, 전시형)
+8월 수련지도 : 응급실 bedside teaching(전시형, 이승주)
+9월 면담 : 수련·진로상담(임창열, 노하경)
+9월 수련지도 : 응급실 초진·신경학적 진찰 지도(노하경, 임창열)</t>
         </is>
       </c>
     </row>
